--- a/TONGUES (1)/Tongues_Outreach_Tracker_LIVE.xlsx
+++ b/TONGUES (1)/Tongues_Outreach_Tracker_LIVE.xlsx
@@ -562,7 +562,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -577,7 +576,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -599,7 +597,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -625,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S92"/>
+  <dimension ref="A1:S108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4594,8 +4591,16 @@
           <t>WeChat emojis + Munich reels</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/27</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Nudge sent 7/27</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
@@ -4638,8 +4643,16 @@
           <t>DALF C1 + Paris student life</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/27</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Nudge sent 7/27</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -4762,9 +4775,6 @@
           <t>BLOCKED - Message button errors (retry later)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -4807,8 +4817,6 @@
           <t>Language journal + C1 goal</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -4851,8 +4859,6 @@
           <t>Day 1 Chinese novels</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -5062,8 +5068,16 @@
           <t>Beijing study diaries</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/27</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Nudge sent 7/27</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
@@ -5106,8 +5120,6 @@
           <t>Travel diaries</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -5150,7 +5162,6 @@
           <t>Zero to fluent in 8 months</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>Unexpected speaker</t>
@@ -5198,7 +5209,6 @@
           <t>62K on 37 posts</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>Seen after send</t>
@@ -5307,7 +5317,6 @@
           <t>French as a place</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>Verified</t>
@@ -5355,8 +5364,6 @@
           <t>IT-in-Japan authenticity</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
@@ -5399,7 +5406,6 @@
           <t>Bio line + 5am skits</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>Unexpected speaker</t>
@@ -5880,6 +5886,858 @@
       <c r="R92" s="9" t="n"/>
       <c r="S92" s="9" t="n"/>
     </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>zosiapiatek</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Zosia Piatek</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Polish creator in Taipei, travel/lifestyle</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>51K</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Albert request 7/27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Between-cultures Poland/Taiwan story</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Unexpected-speaker angle; managed by Mooza (scout@moozamanagement.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>learnspanish.withmarina</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Marina</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Spanish vocab + counting reels</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Kitchenware vocab and counting 5 to 5.555.555 reels</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>hindiwithhitendra</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hitendra</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Hindi via travel/food</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Bohot ho gya / mera pet bhar gya travel food phrases</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>polishwithkamil</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kamil</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Polish made easy</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Learn Polish the easy way bold promise</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>turkishwithirem</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Irem</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Certified Turkish teacher (Yildiz Technical)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>21.1K</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Survive in Turkey with 5 words practicality</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>polishwithblondes</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Duo (2 teachers)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Polish duo, pronunciation</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Two-teacher chemistry, pronunciation breakdowns</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>learnthaiwithnoon</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Jeeranun (Noon)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thai for busy people, 7 min/day</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>113K</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Screen time &amp; cashless payment practical breakdowns</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>tagalogwithkirby</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Tagalog, language-culture-belonging</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>30.7K</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>15 yrs teaching, heritage learners angle</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>learngreekwithkaterina</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Katerina</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Greek is fun, quizzes/dialogues/music</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>8.4K</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Weekly quizzes, dialogues, Greek music energy</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>swedishwithcova</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cova Hedin</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Swedish Latina, Sweden &amp; life</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>40.7K</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Life between borders fresh angle</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>hebrew_with_phil</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Hebrew PhD (Princeton/Columbia/UCLA)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>26.2K</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Sourced 7/26</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Ancient Hebrew pronunciation reels depth</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Re-added after Excel revert; DM sent 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>kiman.viet</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Kim An</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Southern Vietnamese dialect corner</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>1.4K</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/27</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Followed - DM queued</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="9" t="n"/>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="L104" s="9" t="n"/>
+      <c r="M104" s="9" t="n"/>
+      <c r="N104" s="9" t="n"/>
+      <c r="O104" s="9" t="inlineStr">
+        <is>
+          <t>176 likes on 1.4K followers; collab email in bio; dialect angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>beetran1994</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Bee (Hanh Tran)</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Vietnamese + Saigon travel/culture</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>16.3K</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/27</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Followed - DM queued</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="n"/>
+      <c r="I105" s="9" t="n"/>
+      <c r="J105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="L105" s="9" t="n"/>
+      <c r="M105" s="9" t="n"/>
+      <c r="N105" s="9" t="n"/>
+      <c r="O105" s="9" t="inlineStr">
+        <is>
+          <t>Strong engagement; 1:1 lessons; on-camera personality</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>_withsilvia_</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Silvia</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>European Portuguese teacher</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>28.9K</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/27</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>Followed - DM queued</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="L106" s="9" t="n"/>
+      <c r="M106" s="9" t="n"/>
+      <c r="N106" s="9" t="n"/>
+      <c r="O106" s="9" t="inlineStr">
+        <is>
+          <t>1K likes/48 comments recent reel; own courses; PT-PT dialect angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>marcolingual</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Brazilian Portuguese, culture, NYC</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>40.6K</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/27</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>Followed - DM queued</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="n"/>
+      <c r="I107" s="9" t="n"/>
+      <c r="J107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
+      <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
+      <c r="N107" s="9" t="n"/>
+      <c r="O107" s="9" t="inlineStr">
+        <is>
+          <t>5.7K-like pronunciation reel; collab email in bio</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>learnarabicwithasmae</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Asmae</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Arabic for English speakers</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>6.3K</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/27</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>Followed - DM queued</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="n"/>
+      <c r="I108" s="9" t="n"/>
+      <c r="J108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
+      <c r="L108" s="9" t="n"/>
+      <c r="M108" s="9" t="n"/>
+      <c r="N108" s="9" t="n"/>
+      <c r="O108" s="9" t="inlineStr">
+        <is>
+          <t>3M+ YouTube subs cross-platform; 30 dialects reel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/TONGUES (1)/Tongues_Outreach_Tracker_LIVE.xlsx
+++ b/TONGUES (1)/Tongues_Outreach_Tracker_LIVE.xlsx
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S108"/>
+  <dimension ref="A1:S113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1369,11 @@
           <t>Scouse/Geordie breakdowns</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/25</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n">
         <v>5</v>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Dialects = product moat</t>
+          <t>Dialects = product moat; Nudged 7/25 (Sat)</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2498,11 @@
           <t>Shanghainese dialect</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/25</t>
+        </is>
+      </c>
       <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n">
         <v>4</v>
@@ -2507,7 +2515,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Unexpected speaker</t>
+          <t>Unexpected speaker; Nudged 7/25 (Sat)</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2563,11 @@
           <t>Songs in 40+ languages</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/25</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n">
         <v>5</v>
@@ -2568,7 +2580,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Oversized but unique story</t>
+          <t>Oversized but unique story; Nudged 7/25 (Sat)</t>
         </is>
       </c>
     </row>
@@ -4817,6 +4829,16 @@
           <t>Language journal + C1 goal</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/28</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Nudge sent 7/28</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -4857,6 +4879,16 @@
       <c r="I71" t="inlineStr">
         <is>
           <t>Day 1 Chinese novels</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/28</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Nudge sent 7/28</t>
         </is>
       </c>
     </row>
@@ -5120,6 +5152,16 @@
           <t>Travel diaries</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>No reply - nudged 7/28</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Nudge sent 7/28</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -5441,12 +5483,16 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="9" t="inlineStr"/>
-      <c r="J83" s="9" t="inlineStr"/>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K83" s="9" t="n"/>
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
@@ -5486,12 +5532,16 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K84" s="9" t="n"/>
       <c r="L84" s="9" t="n"/>
       <c r="M84" s="9" t="n"/>
@@ -5535,12 +5585,16 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H85" s="9" t="n"/>
       <c r="I85" s="9" t="inlineStr"/>
-      <c r="J85" s="9" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K85" s="9" t="n"/>
       <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
@@ -5580,12 +5634,16 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H86" s="9" t="n"/>
       <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr"/>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K86" s="9" t="n"/>
       <c r="L86" s="9" t="n"/>
       <c r="M86" s="9" t="n"/>
@@ -5629,12 +5687,16 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H87" s="9" t="n"/>
       <c r="I87" s="9" t="inlineStr"/>
-      <c r="J87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K87" s="9" t="n"/>
       <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
@@ -5678,12 +5740,16 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H88" s="9" t="n"/>
       <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="9" t="inlineStr"/>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K88" s="9" t="n"/>
       <c r="L88" s="9" t="n"/>
       <c r="M88" s="9" t="n"/>
@@ -5727,12 +5793,16 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H89" s="9" t="n"/>
       <c r="I89" s="9" t="inlineStr"/>
-      <c r="J89" s="9" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K89" s="9" t="n"/>
       <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
@@ -5776,12 +5846,16 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H90" s="9" t="n"/>
       <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K90" s="9" t="n"/>
       <c r="L90" s="9" t="n"/>
       <c r="M90" s="9" t="n"/>
@@ -5793,45 +5867,49 @@
       <c r="S90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n"/>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>russianwithvladimir</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Vladimir</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>Russian convo coach</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>162K</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Sourced 7/24</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>Followed - DM queued</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="9" t="inlineStr"/>
-      <c r="J91" s="9" t="inlineStr"/>
-      <c r="K91" s="9" t="n"/>
-      <c r="L91" s="9" t="n"/>
-      <c r="M91" s="9" t="n"/>
-      <c r="N91" s="9" t="n"/>
-      <c r="O91" s="9" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>REPLIED - auto-DM (free video training pitch)</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>Auto-reply received - Albert to review</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="n"/>
+      <c r="L91" s="7" t="n"/>
+      <c r="M91" s="7" t="n"/>
+      <c r="N91" s="7" t="n"/>
+      <c r="O91" s="7" t="inlineStr"/>
       <c r="P91" s="9" t="n"/>
       <c r="Q91" s="9" t="n"/>
       <c r="R91" s="9" t="n"/>
@@ -5866,12 +5944,16 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Followed - DM queued</t>
+          <t>DM Sent (earlier run; status lost in revert)</t>
         </is>
       </c>
       <c r="H92" s="9" t="n"/>
       <c r="I92" s="9" t="inlineStr"/>
-      <c r="J92" s="9" t="inlineStr"/>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
       <c r="K92" s="9" t="n"/>
       <c r="L92" s="9" t="n"/>
       <c r="M92" s="9" t="n"/>
@@ -5889,27 +5971,27 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>zosiapiatek</t>
+          <t>learnspanish.withmarina</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Zosia Piatek</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Polish creator in Taipei, travel/lifestyle</t>
+          <t>Spanish vocab + counting reels</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>51K</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Albert request 7/27</t>
+          <t>Sourced 7/26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5924,7 +6006,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Between-cultures Poland/Taiwan story</t>
+          <t>Kitchenware vocab and counting reels</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5939,24 +6021,24 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Unexpected-speaker angle; managed by Mooza (scout@moozamanagement.com)</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>learnspanish.withmarina</t>
+          <t>hindiwithhitendra</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Hitendra</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Spanish vocab + counting reels</t>
+          <t>Hindi via travel/food</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5981,7 +6063,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Kitchenware vocab and counting 5 to 5.555.555 reels</t>
+          <t>Travel food phrases</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5996,24 +6078,24 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>hindiwithhitendra</t>
+          <t>polishwithkamil</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hitendra</t>
+          <t>Kamil</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Hindi via travel/food</t>
+          <t>Polish made easy</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6038,7 +6120,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Bohot ho gya / mera pet bhar gya travel food phrases</t>
+          <t>Learn Polish the easy way bold promise</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6053,29 +6135,29 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>polishwithkamil</t>
+          <t>turkishwithirem</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Irem</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Polish made easy</t>
+          <t>Certified Turkish teacher (Yildiz Technical)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>21.1K</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6095,7 +6177,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Learn Polish the easy way bold promise</t>
+          <t>Survive in Turkey with 5 words</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6110,29 +6192,29 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>turkishwithirem</t>
+          <t>polishwithblondes</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irem</t>
+          <t>Duo (2 teachers)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Certified Turkish teacher (Yildiz Technical)</t>
+          <t>Polish duo, pronunciation</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>21.1K</t>
+          <t>495</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6152,7 +6234,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Survive in Turkey with 5 words practicality</t>
+          <t>Two-teacher chemistry</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6167,29 +6249,29 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>polishwithblondes</t>
+          <t>learnthaiwithnoon</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Duo (2 teachers)</t>
+          <t>Jeeranun (Noon)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Polish duo, pronunciation</t>
+          <t>Thai for busy people, 7 min/day</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>113K</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6209,7 +6291,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Two-teacher chemistry, pronunciation breakdowns</t>
+          <t>Practical daily-life breakdowns</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6224,29 +6306,29 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>learnthaiwithnoon</t>
+          <t>tagalogwithkirby</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jeeranun (Noon)</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thai for busy people, 7 min/day</t>
+          <t>Tagalog, language-culture-belonging</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>113K</t>
+          <t>30.7K</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6266,7 +6348,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Screen time &amp; cashless payment practical breakdowns</t>
+          <t>15 yrs teaching, heritage learners</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6281,29 +6363,29 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>tagalogwithkirby</t>
+          <t>learngreekwithkaterina</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Katerina</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tagalog, language-culture-belonging</t>
+          <t>Greek is fun, quizzes/dialogues/music</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>30.7K</t>
+          <t>8.4K</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6323,7 +6405,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>15 yrs teaching, heritage learners angle</t>
+          <t>Fun energy, quizzes and music</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6338,29 +6420,29 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>learngreekwithkaterina</t>
+          <t>swedishwithcova</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Katerina</t>
+          <t>Cova Hedin</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Greek is fun, quizzes/dialogues/music</t>
+          <t>Swedish Latina, Sweden &amp; life</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>8.4K</t>
+          <t>40.7K</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6380,7 +6462,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Weekly quizzes, dialogues, Greek music energy</t>
+          <t>Life between borders</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6395,29 +6477,29 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>swedishwithcova</t>
+          <t>hebrew_with_phil</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cova Hedin</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Swedish Latina, Sweden &amp; life</t>
+          <t>Hebrew PhD (Princeton/Columbia/UCLA)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>40.7K</t>
+          <t>26.2K</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6437,7 +6519,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Life between borders fresh angle</t>
+          <t>Ancient Hebrew pronunciation depth</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6452,34 +6534,34 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>hebrew_with_phil</t>
+          <t>zosiapiatek</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Zosia Piatek</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hebrew PhD (Princeton/Columbia/UCLA)</t>
+          <t>Polish creator in Taipei, travel/lifestyle</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>26.2K</t>
+          <t>51K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sourced 7/26</t>
+          <t>Albert request 7/27</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6494,7 +6576,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Ancient Hebrew pronunciation reels depth</t>
+          <t>Between-cultures Poland/Taiwan story</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6509,232 +6591,512 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert; DM sent 7/27</t>
+          <t>Unexpected-speaker angle; managed by Mooza (scout@moozamanagement.com)</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="n"/>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>kiman.viet</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Kim An</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>Southern Vietnamese dialect corner</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>1.4K</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>Followed - DM queued</t>
-        </is>
-      </c>
-      <c r="H104" s="9" t="n"/>
-      <c r="I104" s="9" t="n"/>
-      <c r="J104" s="9" t="n"/>
-      <c r="K104" s="9" t="n"/>
-      <c r="L104" s="9" t="n"/>
-      <c r="M104" s="9" t="n"/>
-      <c r="N104" s="9" t="n"/>
-      <c r="O104" s="9" t="inlineStr">
-        <is>
-          <t>176 likes on 1.4K followers; collab email in bio; dialect angle</t>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Southern VN dialect, real Saigon speech</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>8/3</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>beetran1994</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>Bee (Hanh Tran)</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>Vietnamese + Saigon travel/culture</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>16.3K</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>Followed - DM queued</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-      <c r="L105" s="9" t="n"/>
-      <c r="M105" s="9" t="n"/>
-      <c r="N105" s="9" t="n"/>
-      <c r="O105" s="9" t="inlineStr">
-        <is>
-          <t>Strong engagement; 1:1 lessons; on-camera personality</t>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Saigon street food + travel + lessons</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>8/3</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="n"/>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>_withsilvia_</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>Silvia</t>
-        </is>
-      </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>European Portuguese teacher</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>28.9K</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
         </is>
       </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>Followed - DM queued</t>
-        </is>
-      </c>
-      <c r="H106" s="9" t="n"/>
-      <c r="I106" s="9" t="n"/>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
-      <c r="L106" s="9" t="n"/>
-      <c r="M106" s="9" t="n"/>
-      <c r="N106" s="9" t="n"/>
-      <c r="O106" s="9" t="inlineStr">
-        <is>
-          <t>1K likes/48 comments recent reel; own courses; PT-PT dialect angle</t>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>European Portuguese depth, verb reels</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>8/3</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="n"/>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>marcolingual</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>Brazilian Portuguese, culture, NYC</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>40.6K</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
         </is>
       </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>Followed - DM queued</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="n"/>
-      <c r="I107" s="9" t="n"/>
-      <c r="J107" s="9" t="n"/>
-      <c r="K107" s="9" t="n"/>
-      <c r="L107" s="9" t="n"/>
-      <c r="M107" s="9" t="n"/>
-      <c r="N107" s="9" t="n"/>
-      <c r="O107" s="9" t="inlineStr">
-        <is>
-          <t>5.7K-like pronunciation reel; collab email in bio</t>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Brazilian R pronunciation reel</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>8/3</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="n"/>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>learnarabicwithasmae</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Asmae</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>Arabic for English speakers</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>6.3K</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
         </is>
       </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>Followed - DM queued</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="n"/>
-      <c r="I108" s="9" t="n"/>
-      <c r="J108" s="9" t="n"/>
-      <c r="K108" s="9" t="n"/>
-      <c r="L108" s="9" t="n"/>
-      <c r="M108" s="9" t="n"/>
-      <c r="N108" s="9" t="n"/>
-      <c r="O108" s="9" t="inlineStr">
-        <is>
-          <t>3M+ YouTube subs cross-platform; 30 dialects reel</t>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>3M YouTube reach, 30 dialects reel</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>cantoneseafterhours</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Cantonese educator in HK, polyglot</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>10.7K</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/28</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>HK local teaching real Cantonese, dialect angle</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="n"/>
+      <c r="M109" s="9" t="n"/>
+      <c r="N109" s="9" t="n"/>
+      <c r="O109" s="9" t="inlineStr">
+        <is>
+          <t>Followed + DM same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>indonesian_with_suci</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Suci Amalia</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Conversational Indonesian, speak like a local</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>7.7K</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/28</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>Aku pikir alternatives reel, local speech</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="L110" s="9" t="n"/>
+      <c r="M110" s="9" t="n"/>
+      <c r="N110" s="9" t="n"/>
+      <c r="O110" s="9" t="inlineStr">
+        <is>
+          <t>Followed + DM same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>norsk_akademiet</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>NoAk (Yvonne on camera)</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Norwegian academy, viral verb reels</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>18.8K</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/28</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>1.8K-like verb reel, soothing on-camera teaching</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="L111" s="9" t="n"/>
+      <c r="M111" s="9" t="n"/>
+      <c r="N111" s="9" t="n"/>
+      <c r="O111" s="9" t="inlineStr">
+        <is>
+          <t>Followed + DM same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>whatyoumissedintamilclass</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>WYMITC (community)</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>Tamil heritage for diaspora</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>62.1K</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/28</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>Heritage/philosophy angle, spoken vs written Tamil</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="n"/>
+      <c r="M112" s="9" t="n"/>
+      <c r="N112" s="9" t="n"/>
+      <c r="O112" s="9" t="inlineStr">
+        <is>
+          <t>Followed + DM same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>ukrainerka</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Dasha</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Ukrainian teacher, viral relative to size</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>3.7K</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/28</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>1.6K-like reel on 3.7K followers, real local speech</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="n"/>
+      <c r="M113" s="9" t="n"/>
+      <c r="N113" s="9" t="n"/>
+      <c r="O113" s="9" t="inlineStr">
+        <is>
+          <t>Followed + DM same day</t>
         </is>
       </c>
     </row>

--- a/TONGUES (1)/Tongues_Outreach_Tracker_LIVE.xlsx
+++ b/TONGUES (1)/Tongues_Outreach_Tracker_LIVE.xlsx
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:S116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5971,27 +5971,27 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>learnspanish.withmarina</t>
+          <t>ben.overseas</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Ben Silva</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Spanish vocab + counting reels</t>
+          <t>Brit learning Mandarin from 0 in Taipei, Taiwan life</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>24.9K</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sourced 7/26</t>
+          <t>Albert request 7/28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/28</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Kitchenware vocab and counting reels</t>
+          <t>Turned down Cambridge AI PhD, no-regrets-after-cancer story</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6016,29 +6016,29 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/2</t>
+          <t>8/3</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Re-added after Excel revert</t>
+          <t>Learner-creator (not teacher); unexpected-speaker story; TikTok crossover</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>hindiwithhitendra</t>
+          <t>learnspanish.withmarina</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hitendra</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hindi via travel/food</t>
+          <t>Spanish vocab + counting reels</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Travel food phrases</t>
+          <t>Kitchenware vocab and counting reels</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6085,17 +6085,17 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>polishwithkamil</t>
+          <t>hindiwithhitendra</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Hitendra</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Polish made easy</t>
+          <t>Hindi via travel/food</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Learn Polish the easy way bold promise</t>
+          <t>Travel food phrases</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6142,22 +6142,22 @@
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>turkishwithirem</t>
+          <t>polishwithkamil</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irem</t>
+          <t>Kamil</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Certified Turkish teacher (Yildiz Technical)</t>
+          <t>Polish made easy</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>21.1K</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Survive in Turkey with 5 words</t>
+          <t>Learn Polish the easy way bold promise</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6199,22 +6199,22 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>polishwithblondes</t>
+          <t>turkishwithirem</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Duo (2 teachers)</t>
+          <t>Irem</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Polish duo, pronunciation</t>
+          <t>Certified Turkish teacher (Yildiz Technical)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>21.1K</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Two-teacher chemistry</t>
+          <t>Survive in Turkey with 5 words</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6256,22 +6256,22 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>learnthaiwithnoon</t>
+          <t>polishwithblondes</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jeeranun (Noon)</t>
+          <t>Duo (2 teachers)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thai for busy people, 7 min/day</t>
+          <t>Polish duo, pronunciation</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>113K</t>
+          <t>495</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Practical daily-life breakdowns</t>
+          <t>Two-teacher chemistry</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6313,22 +6313,22 @@
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>tagalogwithkirby</t>
+          <t>learnthaiwithnoon</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Jeeranun (Noon)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tagalog, language-culture-belonging</t>
+          <t>Thai for busy people, 7 min/day</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>30.7K</t>
+          <t>113K</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>15 yrs teaching, heritage learners</t>
+          <t>Practical daily-life breakdowns</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6370,22 +6370,22 @@
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>learngreekwithkaterina</t>
+          <t>tagalogwithkirby</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Katerina</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Greek is fun, quizzes/dialogues/music</t>
+          <t>Tagalog, language-culture-belonging</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>8.4K</t>
+          <t>30.7K</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Fun energy, quizzes and music</t>
+          <t>15 yrs teaching, heritage learners</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6427,22 +6427,22 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>swedishwithcova</t>
+          <t>learngreekwithkaterina</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cova Hedin</t>
+          <t>Katerina</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Swedish Latina, Sweden &amp; life</t>
+          <t>Greek is fun, quizzes/dialogues/music</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>40.7K</t>
+          <t>8.4K</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Life between borders</t>
+          <t>Fun energy, quizzes and music</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6484,22 +6484,22 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>hebrew_with_phil</t>
+          <t>swedishwithcova</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Cova Hedin</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Hebrew PhD (Princeton/Columbia/UCLA)</t>
+          <t>Swedish Latina, Sweden &amp; life</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>26.2K</t>
+          <t>40.7K</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Ancient Hebrew pronunciation depth</t>
+          <t>Life between borders</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6541,27 +6541,27 @@
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>zosiapiatek</t>
+          <t>hebrew_with_phil</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Zosia Piatek</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Polish creator in Taipei, travel/lifestyle</t>
+          <t>Hebrew PhD (Princeton/Columbia/UCLA)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>51K</t>
+          <t>26.2K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Albert request 7/27</t>
+          <t>Sourced 7/26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Between-cultures Poland/Taiwan story</t>
+          <t>Ancient Hebrew pronunciation depth</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6591,22 +6591,34 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Unexpected-speaker angle; managed by Mooza (scout@moozamanagement.com)</t>
+          <t>Re-added after Excel revert</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>kiman.viet</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+          <t>zosiapiatek</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Zosia Piatek</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Polish creator in Taipei, travel/lifestyle</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>51K</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sourced 7/27</t>
+          <t>Albert request 7/27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6616,12 +6628,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/27</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Southern VN dialect, real Saigon speech</t>
+          <t>Between-cultures Poland/Taiwan story</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6631,19 +6643,21 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/3</t>
+          <t>8/2</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Unexpected-speaker angle; managed by Mooza (scout@moozamanagement.com)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>beetran1994</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>kiman.viet</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
@@ -6661,7 +6675,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Saigon street food + travel + lessons</t>
+          <t>Southern VN dialect, real Saigon speech</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6678,12 +6692,9 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>_withsilvia_</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>beetran1994</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
@@ -6701,7 +6712,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>European Portuguese depth, verb reels</t>
+          <t>Saigon street food + travel + lessons</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6718,12 +6729,9 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>marcolingual</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+          <t>_withsilvia_</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
@@ -6741,7 +6749,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Brazilian R pronunciation reel</t>
+          <t>European Portuguese depth, verb reels</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6758,101 +6766,74 @@
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
+          <t>marcolingual</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Sourced 7/27</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Brazilian R pronunciation reel</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
           <t>learnarabicwithasmae</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Sourced 7/27</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>DM Sent</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>7/28</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>3M YouTube reach, 30 dialects reel</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>No reply yet</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>8/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="n"/>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>cantoneseafterhours</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>Rachel</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>Cantonese educator in HK, polyglot</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>10.7K</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>Sourced 7/28</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>DM Sent</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
-        <is>
-          <t>7/28</t>
-        </is>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>HK local teaching real Cantonese, dialect angle</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>No reply yet</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr">
-        <is>
-          <t>8/3</t>
-        </is>
-      </c>
-      <c r="L109" s="9" t="n"/>
-      <c r="M109" s="9" t="n"/>
-      <c r="N109" s="9" t="n"/>
-      <c r="O109" s="9" t="inlineStr">
-        <is>
-          <t>Followed + DM same day</t>
         </is>
       </c>
     </row>
@@ -6860,22 +6841,22 @@
       <c r="A110" s="9" t="n"/>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>indonesian_with_suci</t>
+          <t>cantoneseafterhours</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Suci Amalia</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Conversational Indonesian, speak like a local</t>
+          <t>Cantonese educator in HK, polyglot</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>7.7K</t>
+          <t>10.7K</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
@@ -6895,7 +6876,7 @@
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>Aku pikir alternatives reel, local speech</t>
+          <t>HK local teaching real Cantonese, dialect angle</t>
         </is>
       </c>
       <c r="J110" s="9" t="inlineStr">
@@ -6913,7 +6894,7 @@
       <c r="N110" s="9" t="n"/>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>Followed + DM same day</t>
+          <t>Followed + DM same day; follow confirmed 7/28</t>
         </is>
       </c>
     </row>
@@ -6921,22 +6902,22 @@
       <c r="A111" s="9" t="n"/>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>norsk_akademiet</t>
+          <t>indonesian_with_suci</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>NoAk (Yvonne on camera)</t>
+          <t>Suci Amalia</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Norwegian academy, viral verb reels</t>
+          <t>Conversational Indonesian, speak like a local</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>18.8K</t>
+          <t>7.7K</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
@@ -6956,7 +6937,7 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>1.8K-like verb reel, soothing on-camera teaching</t>
+          <t>Aku pikir alternatives reel, local speech</t>
         </is>
       </c>
       <c r="J111" s="9" t="inlineStr">
@@ -6974,7 +6955,7 @@
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>Followed + DM same day</t>
+          <t>Followed + DM same day; follow confirmed 7/28</t>
         </is>
       </c>
     </row>
@@ -6982,22 +6963,22 @@
       <c r="A112" s="9" t="n"/>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>whatyoumissedintamilclass</t>
+          <t>norsk_akademiet</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>WYMITC (community)</t>
+          <t>NoAk (Yvonne on camera)</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Tamil heritage for diaspora</t>
+          <t>Norwegian academy, viral verb reels</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>62.1K</t>
+          <t>18.8K</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
@@ -7017,7 +6998,7 @@
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>Heritage/philosophy angle, spoken vs written Tamil</t>
+          <t>1.8K-like verb reel, soothing on-camera teaching</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr">
@@ -7035,7 +7016,7 @@
       <c r="N112" s="9" t="n"/>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>Followed + DM same day</t>
+          <t>Followed + DM same day; follow confirmed 7/28</t>
         </is>
       </c>
     </row>
@@ -7043,22 +7024,22 @@
       <c r="A113" s="9" t="n"/>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>ukrainerka</t>
+          <t>whatyoumissedintamilclass</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Dasha</t>
+          <t>WYMITC (community)</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Ukrainian teacher, viral relative to size</t>
+          <t>Tamil heritage for diaspora</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>3.7K</t>
+          <t>62.1K</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
@@ -7078,7 +7059,7 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>1.6K-like reel on 3.7K followers, real local speech</t>
+          <t>Heritage/philosophy angle, spoken vs written Tamil</t>
         </is>
       </c>
       <c r="J113" s="9" t="inlineStr">
@@ -7096,7 +7077,190 @@
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="inlineStr">
         <is>
-          <t>Followed + DM same day</t>
+          <t>Followed + DM same day; follow confirmed 7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>ukrainerka</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Dasha</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Ukrainian teacher, viral relative to size</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>3.7K</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Sourced 7/28</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>1.6K-like reel on 3.7K followers, real local speech</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="n"/>
+      <c r="M114" s="9" t="n"/>
+      <c r="N114" s="9" t="n"/>
+      <c r="O114" s="9" t="inlineStr">
+        <is>
+          <t>Followed + DM same day; follow confirmed 7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>weslythomas_</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Wesly Thomas</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>American in Poland, Polish for foreigners, YouTube 105K</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>6.3K IG / 105K YT</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Albert request 8/1</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent + Emailed mgmt</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>8/1</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>Polish city tier list debate; makes Polish feel lived-in not studied</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>8/7</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="n"/>
+      <c r="M115" s="9" t="n"/>
+      <c r="N115" s="9" t="n"/>
+      <c r="O115" s="9" t="inlineStr">
+        <is>
+          <t>Albert is a viewer of his YT channel; verified; already following; talent mgmt whereswes@ruthlesstalent.com; also pianist 2M+ streams; YT-first so cross-platform value; emailed whereswes@ruthlesstalent.com 8/1 from olympianhourglass asking rate for one video + usage rights, brief to follow</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>angelo.develops</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Mens self-improvement, stat-maxxing, lifestyle</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>12.6K</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Albert request 8/1</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>DM Sent</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>8/1</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>10/10 Skills of a Dangerous Man framing; a second language is the stat almost no one maxes and cannot be bought</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>No reply yet</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>8/7</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="n"/>
+      <c r="M116" s="9" t="n"/>
+      <c r="N116" s="9" t="n"/>
+      <c r="O116" s="9" t="inlineStr">
+        <is>
+          <t>Already following; bio link poke.com (AI assistant, not a competitor language app); proven paid-promo creator, runs comment-keyword-to-DM funnels; reels 741-1.5K likes; positioning per Albert: coveted app for men bettering themselves</t>
         </is>
       </c>
     </row>
